--- a/r4-core-140-related-person/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-140-related-person/StructureDefinition-at-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2851" uniqueCount="422">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T11:53:41+00:00</t>
+    <t>2026-10-15T12:52:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -364,7 +364,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -681,7 +681,7 @@
     <t>Practitioner.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -722,6 +722,12 @@
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.type</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.system</t>
@@ -798,7 +804,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -927,10 +933,10 @@
     <t>Practitioner.identifier:vbPK.system</t>
   </si>
   <si>
-    <t>OID for the vbPK in Austria</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.40.0.34.4.22</t>
+    <t>OID for the specific vbPK in Austria</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/core/r4/ValueSet/at-core-vbpk</t>
   </si>
   <si>
     <t>Practitioner.identifier:vbPK.value</t>
@@ -940,27 +946,6 @@
   </si>
   <si>
     <t>Practitioner.identifier:vbPK.assigner</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.id</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.reference</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.type</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.display</t>
-  </si>
-  <si>
-    <t>Bundesministerium für Inneres</t>
   </si>
   <si>
     <t>Practitioner.active</t>
@@ -1058,7 +1043,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address}
+    <t xml:space="preserve">Address {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address}
 </t>
   </si>
   <si>
@@ -1075,6 +1060,10 @@
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
+  </si>
+  <si>
     <t>ORC-24, STF-11, ROL-11, PRT-14</t>
   </si>
   <si>
@@ -1135,7 +1124,7 @@
     <t>AdministrativeGenderAddition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
 </t>
   </si>
   <si>
@@ -1648,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN84"/>
+  <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.5625" customWidth="true" bestFit="true"/>
@@ -1661,7 +1650,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="98.24609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="85.5859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1675,7 +1664,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="46.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -4387,9 +4376,11 @@
       <c r="X24" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y24" s="2"/>
+      <c r="Y24" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4436,7 +4427,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>187</v>
@@ -4465,7 +4456,7 @@
         <v>102</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>189</v>
@@ -4481,7 +4472,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>21</v>
@@ -4552,7 +4543,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>197</v>
@@ -4581,7 +4572,7 @@
         <v>157</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>199</v>
@@ -4666,7 +4657,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>206</v>
@@ -4778,7 +4769,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>214</v>
@@ -4892,10 +4883,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5004,10 +4995,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5118,10 +5109,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5147,13 +5138,13 @@
         <v>157</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5203,7 +5194,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5212,7 +5203,7 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
@@ -5232,10 +5223,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5261,13 +5252,13 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5296,10 +5287,10 @@
         <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5317,7 +5308,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5346,10 +5337,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5375,13 +5366,13 @@
         <v>146</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5431,7 +5422,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5449,7 +5440,7 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -5460,10 +5451,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5489,13 +5480,13 @@
         <v>157</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5503,7 +5494,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>21</v>
@@ -5545,7 +5536,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5574,13 +5565,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>21</v>
@@ -5690,7 +5681,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>156</v>
@@ -5802,7 +5793,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>162</v>
@@ -5916,7 +5907,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>167</v>
@@ -6032,7 +6023,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>177</v>
@@ -6097,9 +6088,11 @@
       <c r="X39" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y39" s="2"/>
+      <c r="Y39" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6146,7 +6139,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>187</v>
@@ -6175,7 +6168,7 @@
         <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M40" t="s" s="2">
         <v>189</v>
@@ -6191,7 +6184,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>21</v>
@@ -6262,7 +6255,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>197</v>
@@ -6376,7 +6369,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>206</v>
@@ -6488,7 +6481,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>214</v>
@@ -6602,10 +6595,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6714,10 +6707,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6828,10 +6821,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6857,13 +6850,13 @@
         <v>157</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6913,7 +6906,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6922,7 +6915,7 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>100</v>
@@ -6942,10 +6935,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6971,13 +6964,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7006,10 +6999,10 @@
         <v>183</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7027,7 +7020,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7056,10 +7049,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7085,13 +7078,13 @@
         <v>146</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7141,7 +7134,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7159,7 +7152,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7170,10 +7163,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7199,13 +7192,13 @@
         <v>157</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7213,7 +7206,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>21</v>
@@ -7255,7 +7248,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7284,13 +7277,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>21</v>
@@ -7300,7 +7293,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -7400,7 +7393,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>156</v>
@@ -7512,7 +7505,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>162</v>
@@ -7626,7 +7619,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>167</v>
@@ -7742,7 +7735,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>177</v>
@@ -7807,9 +7800,11 @@
       <c r="X54" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y54" s="2"/>
+      <c r="Y54" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7856,7 +7851,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>187</v>
@@ -7885,7 +7880,7 @@
         <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>189</v>
@@ -7901,7 +7896,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>296</v>
+        <v>21</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>21</v>
@@ -7919,13 +7914,11 @@
         <v>21</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -7972,7 +7965,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>197</v>
@@ -8086,7 +8079,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>206</v>
@@ -8198,7 +8191,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>214</v>
@@ -8312,10 +8305,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>237</v>
+        <v>302</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8335,23 +8328,29 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>303</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>158</v>
+        <v>304</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q59" s="2"/>
+      <c r="Q59" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="R59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8395,7 +8394,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>160</v>
+        <v>302</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8407,31 +8406,31 @@
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>161</v>
+        <v>309</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>21</v>
+        <v>310</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>239</v>
+        <v>311</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8447,21 +8446,23 @@
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>134</v>
+        <v>312</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>135</v>
+        <v>313</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>163</v>
+        <v>314</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8497,19 +8498,19 @@
         <v>21</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>166</v>
+        <v>311</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8521,16 +8522,16 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>161</v>
+        <v>318</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>21</v>
+        <v>319</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8538,10 +8539,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>241</v>
+        <v>320</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8552,7 +8553,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8564,18 +8565,20 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>157</v>
+        <v>321</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>242</v>
+        <v>322</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>243</v>
+        <v>323</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8623,28 +8626,28 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>245</v>
+        <v>320</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>131</v>
+        <v>327</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -8652,10 +8655,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>248</v>
+        <v>329</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8666,7 +8669,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -8678,18 +8681,20 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>102</v>
+        <v>330</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>249</v>
+        <v>331</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -8713,13 +8718,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -8737,28 +8742,28 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>254</v>
+        <v>329</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>335</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>21</v>
+        <v>336</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>131</v>
+        <v>337</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -8766,10 +8771,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>256</v>
+        <v>339</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8792,18 +8797,18 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>257</v>
+        <v>340</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -8827,13 +8832,13 @@
         <v>21</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -8851,7 +8856,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>260</v>
+        <v>339</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8866,13 +8871,13 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>261</v>
+        <v>346</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -8880,10 +8885,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>305</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>263</v>
+        <v>348</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8903,27 +8908,25 @@
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>157</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>264</v>
+        <v>349</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>306</v>
+        <v>21</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>21</v>
@@ -8965,7 +8968,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>268</v>
+        <v>160</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8977,13 +8980,13 @@
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
@@ -8994,10 +8997,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9008,7 +9011,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9017,29 +9020,23 @@
         <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>308</v>
+        <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>313</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9071,53 +9068,53 @@
         <v>21</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="AC65" s="2"/>
       <c r="AD65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>307</v>
+        <v>166</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>314</v>
+        <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9126,7 +9123,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -9135,23 +9132,19 @@
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>317</v>
+        <v>356</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9199,7 +9192,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>316</v>
+        <v>166</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9208,19 +9201,19 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>323</v>
+        <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>324</v>
+        <v>21</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9228,10 +9221,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9242,7 +9235,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9251,23 +9244,19 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>326</v>
+        <v>157</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9315,28 +9304,28 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>332</v>
+        <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9344,10 +9333,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9358,7 +9347,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -9370,19 +9359,17 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9431,13 +9418,13 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
@@ -9446,13 +9433,13 @@
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9460,10 +9447,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9474,7 +9461,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -9483,20 +9470,20 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>108</v>
+        <v>372</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9521,13 +9508,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9545,13 +9532,13 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
@@ -9560,13 +9547,13 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -9574,10 +9561,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9588,7 +9575,7 @@
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -9600,13 +9587,13 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>157</v>
+        <v>379</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9657,28 +9644,28 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>160</v>
+        <v>378</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>21</v>
+        <v>382</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>21</v>
+        <v>383</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -9686,10 +9673,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9700,7 +9687,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
@@ -9712,13 +9699,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>356</v>
+        <v>158</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>357</v>
+        <v>159</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9757,35 +9744,37 @@
         <v>21</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AC71" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>21</v>
@@ -9796,23 +9785,21 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>21</v>
@@ -9824,15 +9811,17 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>360</v>
+        <v>134</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>361</v>
+        <v>135</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -9890,7 +9879,7 @@
         <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>363</v>
+        <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>139</v>
@@ -9899,7 +9888,7 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>21</v>
@@ -9910,42 +9899,46 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
       </c>
@@ -9993,25 +9986,25 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>21</v>
@@ -10022,10 +10015,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10036,7 +10029,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>21</v>
@@ -10045,20 +10038,20 @@
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>368</v>
+        <v>146</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10107,13 +10100,13 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
@@ -10122,13 +10115,13 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>372</v>
+        <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10136,10 +10129,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10147,10 +10140,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -10162,18 +10155,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>376</v>
+        <v>178</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>379</v>
-      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
       </c>
@@ -10197,13 +10188,13 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>21</v>
+        <v>400</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -10221,13 +10212,13 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
@@ -10239,10 +10230,10 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -10250,10 +10241,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10264,7 +10255,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -10276,16 +10267,18 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>383</v>
+        <v>207</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10333,13 +10326,13 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
@@ -10348,13 +10341,13 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>386</v>
+        <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -10362,10 +10355,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10388,13 +10381,13 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>158</v>
+        <v>411</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>159</v>
+        <v>412</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10445,7 +10438,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>160</v>
+        <v>410</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10457,13 +10450,13 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>161</v>
+        <v>413</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
@@ -10474,14 +10467,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10500,18 +10493,20 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>135</v>
+        <v>415</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>163</v>
+        <v>416</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -10535,13 +10530,13 @@
         <v>21</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>21</v>
@@ -10559,7 +10554,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>166</v>
+        <v>414</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10571,702 +10566,18 @@
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>161</v>
+        <v>420</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>21</v>
+        <v>421</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AN84" t="s" s="2">
         <v>21</v>
       </c>
     </row>
